--- a/model_comb3/EvalOutputs/evaluation_metrics_TestDataset1.xlsx
+++ b/model_comb3/EvalOutputs/evaluation_metrics_TestDataset1.xlsx
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.4545</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2614</v>
+        <v>0.2273</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3433</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="5">
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -512,7 +512,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Seg Threshold used</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -548,7 +558,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0041</v>
+        <v>0.1438</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +568,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0021</v>
+        <v>0.09229999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -588,46 +598,46 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>0.06818200000000001</v>
-      </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0.090909</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>0.295455</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>0.5227270000000001</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>0.340909</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0.568182</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0.613636</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="n">
         <v>0.659091</v>
       </c>
-      <c r="B6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>0.704545</v>
-      </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/model_comb3/EvalOutputs/evaluation_metrics_TestDataset1.xlsx
+++ b/model_comb3/EvalOutputs/evaluation_metrics_TestDataset1.xlsx
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4545</v>
+        <v>0.2727</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2273</v>
+        <v>0.1364</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3125</v>
+        <v>0.2143</v>
       </c>
     </row>
     <row r="5">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001</v>
+        <v>0.4042</v>
       </c>
     </row>
     <row r="4">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1438</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="3">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.3719</v>
       </c>
     </row>
   </sheetData>
@@ -606,19 +606,19 @@
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>0.090909</v>
+        <v>0.022727</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>0.5227270000000001</v>
+        <v>0.318182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>0.568182</v>
+        <v>0.363636</v>
       </c>
     </row>
     <row r="6">
